--- a/data/so-good-apartments/project/sales_comparables.xlsx
+++ b/data/so-good-apartments/project/sales_comparables.xlsx
@@ -7,17 +7,21 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sales Comparables" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sales Comparables'!$A$1:$AG$38</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
+  </numFmts>
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,15 +30,46 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="001F4E78"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F4E78"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E75B6"/>
+        <bgColor rgb="002E75B6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6E4F0"/>
+        <bgColor rgb="00D6E4F0"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -46,19 +81,58 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color rgb="00B4C6E7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B4C6E7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B4C6E7"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -425,204 +499,4628 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:AG38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="25" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
+    <col width="26" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
+    <col width="26" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="23" customWidth="1" min="20" max="20"/>
+    <col width="31" customWidth="1" min="21" max="21"/>
+    <col width="21" customWidth="1" min="22" max="22"/>
+    <col width="17" customWidth="1" min="23" max="23"/>
+    <col width="25" customWidth="1" min="24" max="24"/>
+    <col width="25" customWidth="1" min="25" max="25"/>
+    <col width="25" customWidth="1" min="26" max="26"/>
+    <col width="34" customWidth="1" min="27" max="27"/>
+    <col width="27" customWidth="1" min="28" max="28"/>
+    <col width="9" customWidth="1" min="29" max="29"/>
+    <col width="23" customWidth="1" min="30" max="30"/>
+    <col width="20" customWidth="1" min="31" max="31"/>
+    <col width="18" customWidth="1" min="32" max="32"/>
+    <col width="18" customWidth="1" min="33" max="33"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Property Name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
+          <t>Sales Comparables – Springfield MSA Multifamily</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Comp Name</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Address</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Zip Code</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Sale Date</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Sale Price</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Price Per Unit</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Year Built</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Sale Price</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Price Per Unit</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Cap Rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>The Aster</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>3611 Congress Ave</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Sep-24</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>2021</v>
-      </c>
-      <c r="E2" t="n">
-        <v>270</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>$105600000</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>$391111</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>4.50%</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Novel Turtle Creek</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>4251 Irving Ave</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Dec-23</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>2022</v>
-      </c>
-      <c r="E3" t="n">
-        <v>206</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>$74100000</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>$359709</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>4.70%</t>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Renovation Year</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Property Type</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Property Class</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Occupancy at Sale (%)</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>Cap Rate at Sale (%)</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>Pro Forma Cap Rate (%)</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>NOI at Sale</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>Average Unit Size (SF)</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>Price Per SF</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>Market Submarket</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>Distance to Subject (miles)</t>
+        </is>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Construction Type</t>
+        </is>
+      </c>
+      <c r="W3" s="2" t="inlineStr">
+        <is>
+          <t>Parking Ratio</t>
+        </is>
+      </c>
+      <c r="X3" s="2" t="inlineStr">
+        <is>
+          <t>Amenities Score (1-5)</t>
+        </is>
+      </c>
+      <c r="Y3" s="2" t="inlineStr">
+        <is>
+          <t>Average Rent Per Unit</t>
+        </is>
+      </c>
+      <c r="Z3" s="2" t="inlineStr">
+        <is>
+          <t>Rent Per SF Per Month</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
+          <t>Rent Growth Last 12 Months (%)</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>Concessions at Sale (%)</t>
+        </is>
+      </c>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>GRM</t>
+        </is>
+      </c>
+      <c r="AD3" s="2" t="inlineStr">
+        <is>
+          <t>Asset Quality (1-5)</t>
+        </is>
+      </c>
+      <c r="AE3" s="2" t="inlineStr">
+        <is>
+          <t>Transaction Type</t>
+        </is>
+      </c>
+      <c r="AF3" s="2" t="inlineStr">
+        <is>
+          <t>Buyer Type</t>
+        </is>
+      </c>
+      <c r="AG3" s="2" t="inlineStr">
+        <is>
+          <t>Seller Type</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>The Laurel</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>8600 Preston Rd</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Apr-23</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>2019</v>
-      </c>
-      <c r="E4" t="n">
-        <v>159</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>$77275000</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>$486006</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>4.00%</t>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Riverbend Residences</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>123 Waterfront Dr</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Springfield</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>62701</v>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>2023-11-15</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>72500000</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>320</v>
+      </c>
+      <c r="I4" s="7" t="n">
+        <v>226562.5</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>2018</v>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>Class A</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>Luxury</t>
+        </is>
+      </c>
+      <c r="N4" s="7" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="O4" s="7" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="P4" s="7" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="Q4" s="5" t="n">
+        <v>3443750</v>
+      </c>
+      <c r="R4" s="5" t="n">
+        <v>980</v>
+      </c>
+      <c r="S4" s="7" t="n">
+        <v>231.19</v>
+      </c>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>Downtown Riverfront</t>
+        </is>
+      </c>
+      <c r="U4" s="7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V4" s="4" t="inlineStr">
+        <is>
+          <t>Wood Frame</t>
+        </is>
+      </c>
+      <c r="W4" s="7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X4" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y4" s="5" t="n">
+        <v>1950</v>
+      </c>
+      <c r="Z4" s="7" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AA4" s="7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AB4" s="7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC4" s="7" t="n">
+        <v>9.68</v>
+      </c>
+      <c r="AD4" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE4" s="4" t="inlineStr">
+        <is>
+          <t>Arm's Length</t>
+        </is>
+      </c>
+      <c r="AF4" s="4" t="inlineStr">
+        <is>
+          <t>Institutional</t>
+        </is>
+      </c>
+      <c r="AG4" s="4" t="inlineStr">
+        <is>
+          <t>Developer</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>AMLI Design Dist</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>1400 Hi Line Dr</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Sep-23</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Cityscape Towers</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>450 Metro Ave</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Springfield</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>62704</v>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>68000000</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>290</v>
+      </c>
+      <c r="I5" s="12" t="n">
+        <v>234482.76</v>
+      </c>
+      <c r="J5" s="10" t="n">
+        <v>2020</v>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L5" s="9" t="inlineStr">
+        <is>
+          <t>Class A</t>
+        </is>
+      </c>
+      <c r="M5" s="9" t="inlineStr">
+        <is>
+          <t>Luxury</t>
+        </is>
+      </c>
+      <c r="N5" s="12" t="n">
+        <v>97</v>
+      </c>
+      <c r="O5" s="12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P5" s="12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Q5" s="10" t="n">
+        <v>3128000</v>
+      </c>
+      <c r="R5" s="10" t="n">
+        <v>920</v>
+      </c>
+      <c r="S5" s="12" t="n">
+        <v>240.23</v>
+      </c>
+      <c r="T5" s="9" t="inlineStr">
+        <is>
+          <t>Midtown Core</t>
+        </is>
+      </c>
+      <c r="U5" s="12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="V5" s="9" t="inlineStr">
+        <is>
+          <t>Steel Frame</t>
+        </is>
+      </c>
+      <c r="W5" s="12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X5" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y5" s="10" t="n">
+        <v>2050</v>
+      </c>
+      <c r="Z5" s="12" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AA5" s="12" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AB5" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC5" s="12" t="n">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="AD5" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE5" s="9" t="inlineStr">
+        <is>
+          <t>Arm's Length</t>
+        </is>
+      </c>
+      <c r="AF5" s="9" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="AG5" s="9" t="inlineStr">
+        <is>
+          <t>Institutional</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Parkside Lofts</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>789 Green Blvd</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Springfield</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>62707</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>2023-12-05</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>58500000</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>260</v>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>225000</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>2017</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>2022</v>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>Class A</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>Mid-Market</t>
+        </is>
+      </c>
+      <c r="N6" s="7" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="O6" s="7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="P6" s="7" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Q6" s="5" t="n">
+        <v>2983500</v>
+      </c>
+      <c r="R6" s="5" t="n">
+        <v>950</v>
+      </c>
+      <c r="S6" s="7" t="n">
+        <v>236.75</v>
+      </c>
+      <c r="T6" s="4" t="inlineStr">
+        <is>
+          <t>Uptown Greens</t>
+        </is>
+      </c>
+      <c r="U6" s="7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V6" s="4" t="inlineStr">
+        <is>
+          <t>Wood Frame</t>
+        </is>
+      </c>
+      <c r="W6" s="7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X6" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y6" s="5" t="n">
+        <v>1875</v>
+      </c>
+      <c r="Z6" s="7" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AA6" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB6" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC6" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD6" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE6" s="4" t="inlineStr">
+        <is>
+          <t>Arm's Length</t>
+        </is>
+      </c>
+      <c r="AF6" s="4" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="AG6" s="4" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Grandview Apartments</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>101 Summit Rd</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Springfield</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>62703</v>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>63000000</v>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>310</v>
+      </c>
+      <c r="I7" s="12" t="n">
+        <v>203225.81</v>
+      </c>
+      <c r="J7" s="10" t="n">
+        <v>2005</v>
+      </c>
+      <c r="K7" s="10" t="n">
+        <v>2019</v>
+      </c>
+      <c r="L7" s="9" t="inlineStr">
+        <is>
+          <t>Class B+</t>
+        </is>
+      </c>
+      <c r="M7" s="9" t="inlineStr">
+        <is>
+          <t>Mid-Market</t>
+        </is>
+      </c>
+      <c r="N7" s="12" t="n">
+        <v>94</v>
+      </c>
+      <c r="O7" s="12" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="P7" s="12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Q7" s="10" t="n">
+        <v>3370500</v>
+      </c>
+      <c r="R7" s="10" t="n">
+        <v>900</v>
+      </c>
+      <c r="S7" s="12" t="n">
+        <v>226.03</v>
+      </c>
+      <c r="T7" s="9" t="inlineStr">
+        <is>
+          <t>South Hills</t>
+        </is>
+      </c>
+      <c r="U7" s="12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="V7" s="9" t="inlineStr">
+        <is>
+          <t>Wood Frame</t>
+        </is>
+      </c>
+      <c r="W7" s="12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X7" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y7" s="10" t="n">
+        <v>1750</v>
+      </c>
+      <c r="Z7" s="12" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AA7" s="12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB7" s="12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC7" s="12" t="n">
+        <v>9.69</v>
+      </c>
+      <c r="AD7" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE7" s="9" t="inlineStr">
+        <is>
+          <t>Arm's Length</t>
+        </is>
+      </c>
+      <c r="AF7" s="9" t="inlineStr">
+        <is>
+          <t>REIT</t>
+        </is>
+      </c>
+      <c r="AG7" s="9" t="inlineStr">
+        <is>
+          <t>Institutional</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>The Preserve at Willow Creek</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>200 Nature Ln</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Springfield</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>62708</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>78000000</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>222857.14</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>2021</v>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>Class A</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>Luxury</t>
+        </is>
+      </c>
+      <c r="N8" s="7" t="n">
+        <v>98</v>
+      </c>
+      <c r="O8" s="7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P8" s="7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Q8" s="5" t="n">
+        <v>3510000</v>
+      </c>
+      <c r="R8" s="5" t="n">
+        <v>1020</v>
+      </c>
+      <c r="S8" s="7" t="n">
+        <v>219.47</v>
+      </c>
+      <c r="T8" s="4" t="inlineStr">
+        <is>
+          <t>Northwood Estates</t>
+        </is>
+      </c>
+      <c r="U8" s="7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="V8" s="4" t="inlineStr">
+        <is>
+          <t>Wood Frame</t>
+        </is>
+      </c>
+      <c r="W8" s="7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X8" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y8" s="5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="Z8" s="7" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AA8" s="7" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AB8" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC8" s="7" t="n">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="AD8" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE8" s="4" t="inlineStr">
+        <is>
+          <t>Arm's Length</t>
+        </is>
+      </c>
+      <c r="AF8" s="4" t="inlineStr">
+        <is>
+          <t>Institutional</t>
+        </is>
+      </c>
+      <c r="AG8" s="4" t="inlineStr">
+        <is>
+          <t>Developer</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Lakeshore Pointe</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>333 Lakeview Dr</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Springfield</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>62701</v>
+      </c>
+      <c r="F9" s="11" t="inlineStr">
+        <is>
+          <t>2023-07-11</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="n">
+        <v>54000000</v>
+      </c>
+      <c r="H9" s="10" t="n">
+        <v>280</v>
+      </c>
+      <c r="I9" s="12" t="n">
+        <v>192857.14</v>
+      </c>
+      <c r="J9" s="10" t="n">
+        <v>1998</v>
+      </c>
+      <c r="K9" s="10" t="n">
+        <v>2015</v>
+      </c>
+      <c r="L9" s="9" t="inlineStr">
+        <is>
+          <t>Class B</t>
+        </is>
+      </c>
+      <c r="M9" s="9" t="inlineStr">
+        <is>
+          <t>Workforce</t>
+        </is>
+      </c>
+      <c r="N9" s="12" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="O9" s="12" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="P9" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q9" s="10" t="n">
+        <v>3132000</v>
+      </c>
+      <c r="R9" s="10" t="n">
+        <v>880</v>
+      </c>
+      <c r="S9" s="12" t="n">
+        <v>219.16</v>
+      </c>
+      <c r="T9" s="9" t="inlineStr">
+        <is>
+          <t>Waterfront South</t>
+        </is>
+      </c>
+      <c r="U9" s="12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="V9" s="9" t="inlineStr">
+        <is>
+          <t>Concrete</t>
+        </is>
+      </c>
+      <c r="W9" s="12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X9" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y9" s="10" t="n">
+        <v>1550</v>
+      </c>
+      <c r="Z9" s="12" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AA9" s="12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB9" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC9" s="12" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="AD9" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE9" s="9" t="inlineStr">
+        <is>
+          <t>Arm's Length</t>
+        </is>
+      </c>
+      <c r="AF9" s="9" t="inlineStr">
+        <is>
+          <t>Individual</t>
+        </is>
+      </c>
+      <c r="AG9" s="9" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Summit View</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>606 Mountain Way</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Springfield</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>62704</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>2023-06-25</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>60500000</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>275</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>220000</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>2019</v>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>Class A</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>Mid-Market</t>
+        </is>
+      </c>
+      <c r="N10" s="7" t="n">
+        <v>96</v>
+      </c>
+      <c r="O10" s="7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P10" s="7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="Q10" s="5" t="n">
+        <v>2964500</v>
+      </c>
+      <c r="R10" s="5" t="n">
+        <v>960</v>
+      </c>
+      <c r="S10" s="7" t="n">
+        <v>230.14</v>
+      </c>
+      <c r="T10" s="4" t="inlineStr">
+        <is>
+          <t>Midtown Heights</t>
+        </is>
+      </c>
+      <c r="U10" s="7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="V10" s="4" t="inlineStr">
+        <is>
+          <t>Wood Frame</t>
+        </is>
+      </c>
+      <c r="W10" s="7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X10" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y10" s="5" t="n">
+        <v>1900</v>
+      </c>
+      <c r="Z10" s="7" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AA10" s="7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AB10" s="7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC10" s="7" t="n">
+        <v>9.66</v>
+      </c>
+      <c r="AD10" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE10" s="4" t="inlineStr">
+        <is>
+          <t>Arm's Length</t>
+        </is>
+      </c>
+      <c r="AF10" s="4" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="AG10" s="4" t="inlineStr">
+        <is>
+          <t>Developer</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Green Valley Flats</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>112 Meadow Ct</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Springfield</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>62707</v>
+      </c>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>2023-05-18</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="n">
+        <v>51000000</v>
+      </c>
+      <c r="H11" s="10" t="n">
+        <v>250</v>
+      </c>
+      <c r="I11" s="12" t="n">
+        <v>204000</v>
+      </c>
+      <c r="J11" s="10" t="n">
+        <v>2008</v>
+      </c>
+      <c r="K11" s="10" t="n">
         <v>2018</v>
       </c>
-      <c r="E5" t="n">
-        <v>314</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>$97000000</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>$308917</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>4.80%</t>
+      <c r="L11" s="9" t="inlineStr">
+        <is>
+          <t>Class B+</t>
+        </is>
+      </c>
+      <c r="M11" s="9" t="inlineStr">
+        <is>
+          <t>Mid-Market</t>
+        </is>
+      </c>
+      <c r="N11" s="12" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="O11" s="12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="P11" s="12" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="Q11" s="10" t="n">
+        <v>2805000</v>
+      </c>
+      <c r="R11" s="10" t="n">
+        <v>910</v>
+      </c>
+      <c r="S11" s="12" t="n">
+        <v>224.18</v>
+      </c>
+      <c r="T11" s="9" t="inlineStr">
+        <is>
+          <t>Uptown West</t>
+        </is>
+      </c>
+      <c r="U11" s="12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V11" s="9" t="inlineStr">
+        <is>
+          <t>Wood Frame</t>
+        </is>
+      </c>
+      <c r="W11" s="12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X11" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y11" s="10" t="n">
+        <v>1680</v>
+      </c>
+      <c r="Z11" s="12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA11" s="12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB11" s="12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC11" s="12" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="AD11" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE11" s="9" t="inlineStr">
+        <is>
+          <t>Arm's Length</t>
+        </is>
+      </c>
+      <c r="AF11" s="9" t="inlineStr">
+        <is>
+          <t>REIT</t>
+        </is>
+      </c>
+      <c r="AG11" s="9" t="inlineStr">
+        <is>
+          <t>Individual</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Cedar Ridge Apartments</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>88 Forest Rd</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Springfield</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>62703</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>2023-04-03</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>69500000</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>330</v>
+      </c>
+      <c r="I12" s="7" t="n">
+        <v>210606.06</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>2016</v>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>Class A</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>Luxury</t>
+        </is>
+      </c>
+      <c r="N12" s="7" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="O12" s="7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P12" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q12" s="5" t="n">
+        <v>3336000</v>
+      </c>
+      <c r="R12" s="5" t="n">
+        <v>990</v>
+      </c>
+      <c r="S12" s="7" t="n">
+        <v>212.73</v>
+      </c>
+      <c r="T12" s="4" t="inlineStr">
+        <is>
+          <t>South Ridge</t>
+        </is>
+      </c>
+      <c r="U12" s="7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="V12" s="4" t="inlineStr">
+        <is>
+          <t>Wood Frame</t>
+        </is>
+      </c>
+      <c r="W12" s="7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X12" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y12" s="5" t="n">
+        <v>1890</v>
+      </c>
+      <c r="Z12" s="7" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA12" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB12" s="7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC12" s="7" t="n">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="AD12" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE12" s="4" t="inlineStr">
+        <is>
+          <t>Arm's Length</t>
+        </is>
+      </c>
+      <c r="AF12" s="4" t="inlineStr">
+        <is>
+          <t>Institutional</t>
+        </is>
+      </c>
+      <c r="AG12" s="4" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Metropolitan Place</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>222 Commerce St</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Springfield</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>62704</v>
+      </c>
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>2023-03-22</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="n">
+        <v>66000000</v>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="I13" s="12" t="n">
+        <v>220000</v>
+      </c>
+      <c r="J13" s="10" t="n">
+        <v>2022</v>
+      </c>
+      <c r="K13" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L13" s="9" t="inlineStr">
+        <is>
+          <t>Class A</t>
+        </is>
+      </c>
+      <c r="M13" s="9" t="inlineStr">
+        <is>
+          <t>Luxury</t>
+        </is>
+      </c>
+      <c r="N13" s="12" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="O13" s="12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="P13" s="12" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="Q13" s="10" t="n">
+        <v>3102000</v>
+      </c>
+      <c r="R13" s="10" t="n">
+        <v>930</v>
+      </c>
+      <c r="S13" s="12" t="n">
+        <v>236.56</v>
+      </c>
+      <c r="T13" s="9" t="inlineStr">
+        <is>
+          <t>Midtown Core</t>
+        </is>
+      </c>
+      <c r="U13" s="12" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V13" s="9" t="inlineStr">
+        <is>
+          <t>Steel Frame</t>
+        </is>
+      </c>
+      <c r="W13" s="12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X13" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y13" s="10" t="n">
+        <v>2000</v>
+      </c>
+      <c r="Z13" s="12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA13" s="12" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AB13" s="12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC13" s="12" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="AD13" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE13" s="9" t="inlineStr">
+        <is>
+          <t>Arm's Length</t>
+        </is>
+      </c>
+      <c r="AF13" s="9" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="AG13" s="9" t="inlineStr">
+        <is>
+          <t>Developer</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>The Regency at Elm Street</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>555 Elm St</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Springfield</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>62701</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>2023-02-14</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>48000000</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>240</v>
+      </c>
+      <c r="I14" s="7" t="n">
+        <v>200000</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>1995</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>2016</v>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>Class B</t>
+        </is>
+      </c>
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>Workforce</t>
+        </is>
+      </c>
+      <c r="N14" s="7" t="n">
+        <v>92</v>
+      </c>
+      <c r="O14" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="P14" s="7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="Q14" s="5" t="n">
+        <v>2880000</v>
+      </c>
+      <c r="R14" s="5" t="n">
+        <v>850</v>
+      </c>
+      <c r="S14" s="7" t="n">
+        <v>235.29</v>
+      </c>
+      <c r="T14" s="4" t="inlineStr">
+        <is>
+          <t>Downtown East</t>
+        </is>
+      </c>
+      <c r="U14" s="7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V14" s="4" t="inlineStr">
+        <is>
+          <t>Brick</t>
+        </is>
+      </c>
+      <c r="W14" s="7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X14" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y14" s="5" t="n">
+        <v>1450</v>
+      </c>
+      <c r="Z14" s="7" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AA14" s="7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB14" s="7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AC14" s="7" t="n">
+        <v>11.49</v>
+      </c>
+      <c r="AD14" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE14" s="4" t="inlineStr">
+        <is>
+          <t>Arm's Length</t>
+        </is>
+      </c>
+      <c r="AF14" s="4" t="inlineStr">
+        <is>
+          <t>Individual</t>
+        </is>
+      </c>
+      <c r="AG14" s="4" t="inlineStr">
+        <is>
+          <t>Individual</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Heritage Crossing</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>777 Old Town Rd</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Springfield</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>62707</v>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>2023-01-09</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="n">
+        <v>56000000</v>
+      </c>
+      <c r="H15" s="10" t="n">
+        <v>285</v>
+      </c>
+      <c r="I15" s="12" t="n">
+        <v>196491.23</v>
+      </c>
+      <c r="J15" s="10" t="n">
+        <v>2002</v>
+      </c>
+      <c r="K15" s="10" t="n">
+        <v>2017</v>
+      </c>
+      <c r="L15" s="9" t="inlineStr">
+        <is>
+          <t>Class B+</t>
+        </is>
+      </c>
+      <c r="M15" s="9" t="inlineStr">
+        <is>
+          <t>Mid-Market</t>
+        </is>
+      </c>
+      <c r="N15" s="12" t="n">
+        <v>95</v>
+      </c>
+      <c r="O15" s="12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="P15" s="12" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="Q15" s="10" t="n">
+        <v>2912000</v>
+      </c>
+      <c r="R15" s="10" t="n">
+        <v>920</v>
+      </c>
+      <c r="S15" s="12" t="n">
+        <v>210.02</v>
+      </c>
+      <c r="T15" s="9" t="inlineStr">
+        <is>
+          <t>Uptown Historical</t>
+        </is>
+      </c>
+      <c r="U15" s="12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V15" s="9" t="inlineStr">
+        <is>
+          <t>Wood Frame</t>
+        </is>
+      </c>
+      <c r="W15" s="12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X15" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y15" s="10" t="n">
+        <v>1700</v>
+      </c>
+      <c r="Z15" s="12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA15" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB15" s="12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC15" s="12" t="n">
+        <v>9.66</v>
+      </c>
+      <c r="AD15" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE15" s="9" t="inlineStr">
+        <is>
+          <t>Arm's Length</t>
+        </is>
+      </c>
+      <c r="AF15" s="9" t="inlineStr">
+        <is>
+          <t>REIT</t>
+        </is>
+      </c>
+      <c r="AG15" s="9" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Waterfront Walk</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>800 Marina Way</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Springfield</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>62701</v>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>2022-12-10</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>75000000</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>340</v>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>220588.24</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>2021</v>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>Class A</t>
+        </is>
+      </c>
+      <c r="M16" s="4" t="inlineStr">
+        <is>
+          <t>Luxury</t>
+        </is>
+      </c>
+      <c r="N16" s="7" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="O16" s="7" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="P16" s="7" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="Q16" s="5" t="n">
+        <v>3487500</v>
+      </c>
+      <c r="R16" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="S16" s="7" t="n">
+        <v>220.59</v>
+      </c>
+      <c r="T16" s="4" t="inlineStr">
+        <is>
+          <t>Downtown Riverfront</t>
+        </is>
+      </c>
+      <c r="U16" s="7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V16" s="4" t="inlineStr">
+        <is>
+          <t>Wood Frame</t>
+        </is>
+      </c>
+      <c r="W16" s="7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X16" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y16" s="5" t="n">
+        <v>1980</v>
+      </c>
+      <c r="Z16" s="7" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AA16" s="7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AB16" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AC16" s="7" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AD16" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE16" s="4" t="inlineStr">
+        <is>
+          <t>Arm's Length</t>
+        </is>
+      </c>
+      <c r="AF16" s="4" t="inlineStr">
+        <is>
+          <t>Institutional</t>
+        </is>
+      </c>
+      <c r="AG16" s="4" t="inlineStr">
+        <is>
+          <t>Developer</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>The Commons at Maple Ave</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>111 Maple Ave</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Springfield</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>62703</v>
+      </c>
+      <c r="F17" s="11" t="inlineStr">
+        <is>
+          <t>2022-11-28</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="n">
+        <v>62000000</v>
+      </c>
+      <c r="H17" s="10" t="n">
+        <v>305</v>
+      </c>
+      <c r="I17" s="12" t="n">
+        <v>203278.69</v>
+      </c>
+      <c r="J17" s="10" t="n">
+        <v>2010</v>
+      </c>
+      <c r="K17" s="10" t="n">
+        <v>2020</v>
+      </c>
+      <c r="L17" s="9" t="inlineStr">
+        <is>
+          <t>Class B+</t>
+        </is>
+      </c>
+      <c r="M17" s="9" t="inlineStr">
+        <is>
+          <t>Mid-Market</t>
+        </is>
+      </c>
+      <c r="N17" s="12" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="O17" s="12" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="P17" s="12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="Q17" s="10" t="n">
+        <v>3131000</v>
+      </c>
+      <c r="R17" s="10" t="n">
+        <v>940</v>
+      </c>
+      <c r="S17" s="12" t="n">
+        <v>216.25</v>
+      </c>
+      <c r="T17" s="9" t="inlineStr">
+        <is>
+          <t>Southwood</t>
+        </is>
+      </c>
+      <c r="U17" s="12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V17" s="9" t="inlineStr">
+        <is>
+          <t>Wood Frame</t>
+        </is>
+      </c>
+      <c r="W17" s="12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X17" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y17" s="10" t="n">
+        <v>1780</v>
+      </c>
+      <c r="Z17" s="12" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AA17" s="12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AB17" s="12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC17" s="12" t="n">
+        <v>9.51</v>
+      </c>
+      <c r="AD17" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE17" s="9" t="inlineStr">
+        <is>
+          <t>Arm's Length</t>
+        </is>
+      </c>
+      <c r="AF17" s="9" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="AG17" s="9" t="inlineStr">
+        <is>
+          <t>Individual</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Briarwood Estates</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>444 Stone Ln</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Springfield</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>62708</v>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>2022-10-17</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>70000000</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>315</v>
+      </c>
+      <c r="I18" s="7" t="n">
+        <v>222222.22</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>2019</v>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>Class A</t>
+        </is>
+      </c>
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t>Luxury</t>
+        </is>
+      </c>
+      <c r="N18" s="7" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="O18" s="7" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="P18" s="7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Q18" s="5" t="n">
+        <v>3304000</v>
+      </c>
+      <c r="R18" s="5" t="n">
+        <v>1010</v>
+      </c>
+      <c r="S18" s="7" t="n">
+        <v>219.98</v>
+      </c>
+      <c r="T18" s="4" t="inlineStr">
+        <is>
+          <t>Northwood Hills</t>
+        </is>
+      </c>
+      <c r="U18" s="7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="V18" s="4" t="inlineStr">
+        <is>
+          <t>Wood Frame</t>
+        </is>
+      </c>
+      <c r="W18" s="7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X18" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y18" s="5" t="n">
+        <v>2020</v>
+      </c>
+      <c r="Z18" s="7" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AA18" s="7" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="AB18" s="7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC18" s="7" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="AD18" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE18" s="4" t="inlineStr">
+        <is>
+          <t>Arm's Length</t>
+        </is>
+      </c>
+      <c r="AF18" s="4" t="inlineStr">
+        <is>
+          <t>Institutional</t>
+        </is>
+      </c>
+      <c r="AG18" s="4" t="inlineStr">
+        <is>
+          <t>Developer</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>Oakhaven Apartments</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>99 Oakwood Dr</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Springfield</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>62707</v>
+      </c>
+      <c r="F19" s="11" t="inlineStr">
+        <is>
+          <t>2022-09-01</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="n">
+        <v>53000000</v>
+      </c>
+      <c r="H19" s="10" t="n">
+        <v>265</v>
+      </c>
+      <c r="I19" s="12" t="n">
+        <v>200000</v>
+      </c>
+      <c r="J19" s="10" t="n">
+        <v>2000</v>
+      </c>
+      <c r="K19" s="10" t="n">
+        <v>2016</v>
+      </c>
+      <c r="L19" s="9" t="inlineStr">
+        <is>
+          <t>Class B</t>
+        </is>
+      </c>
+      <c r="M19" s="9" t="inlineStr">
+        <is>
+          <t>Mid-Market</t>
+        </is>
+      </c>
+      <c r="N19" s="12" t="n">
+        <v>93</v>
+      </c>
+      <c r="O19" s="12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="P19" s="12" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Q19" s="10" t="n">
+        <v>2968000</v>
+      </c>
+      <c r="R19" s="10" t="n">
+        <v>890</v>
+      </c>
+      <c r="S19" s="12" t="n">
+        <v>224.72</v>
+      </c>
+      <c r="T19" s="9" t="inlineStr">
+        <is>
+          <t>Uptown East</t>
+        </is>
+      </c>
+      <c r="U19" s="12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="V19" s="9" t="inlineStr">
+        <is>
+          <t>Wood Frame</t>
+        </is>
+      </c>
+      <c r="W19" s="12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X19" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y19" s="10" t="n">
+        <v>1600</v>
+      </c>
+      <c r="Z19" s="12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA19" s="12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB19" s="12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AC19" s="12" t="n">
+        <v>10.42</v>
+      </c>
+      <c r="AD19" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE19" s="9" t="inlineStr">
+        <is>
+          <t>Arm's Length</t>
+        </is>
+      </c>
+      <c r="AF19" s="9" t="inlineStr">
+        <is>
+          <t>Individual</t>
+        </is>
+      </c>
+      <c r="AG19" s="9" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Emerald Pointe</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>121 Gemstone Cir</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Springfield</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>62704</v>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>2022-08-15</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>67000000</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>310</v>
+      </c>
+      <c r="I20" s="7" t="n">
+        <v>216129.03</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>2020</v>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>Class A</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>Mid-Market</t>
+        </is>
+      </c>
+      <c r="N20" s="7" t="n">
+        <v>97</v>
+      </c>
+      <c r="O20" s="7" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="P20" s="7" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="Q20" s="5" t="n">
+        <v>3270000</v>
+      </c>
+      <c r="R20" s="5" t="n">
+        <v>950</v>
+      </c>
+      <c r="S20" s="7" t="n">
+        <v>227.49</v>
+      </c>
+      <c r="T20" s="4" t="inlineStr">
+        <is>
+          <t>Midtown West</t>
+        </is>
+      </c>
+      <c r="U20" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V20" s="4" t="inlineStr">
+        <is>
+          <t>Steel Frame</t>
+        </is>
+      </c>
+      <c r="W20" s="7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X20" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y20" s="5" t="n">
+        <v>1920</v>
+      </c>
+      <c r="Z20" s="7" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AA20" s="7" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AB20" s="7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC20" s="7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD20" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE20" s="4" t="inlineStr">
+        <is>
+          <t>Arm's Length</t>
+        </is>
+      </c>
+      <c r="AF20" s="4" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="AG20" s="4" t="inlineStr">
+        <is>
+          <t>Developer</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Horizon Heights</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>888 Sky St</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Springfield</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>62701</v>
+      </c>
+      <c r="F21" s="11" t="inlineStr">
+        <is>
+          <t>2022-07-28</t>
+        </is>
+      </c>
+      <c r="G21" s="10" t="n">
+        <v>71000000</v>
+      </c>
+      <c r="H21" s="10" t="n">
+        <v>330</v>
+      </c>
+      <c r="I21" s="12" t="n">
+        <v>215151.52</v>
+      </c>
+      <c r="J21" s="10" t="n">
+        <v>2018</v>
+      </c>
+      <c r="K21" s="10" t="n">
+        <v>2023</v>
+      </c>
+      <c r="L21" s="9" t="inlineStr">
+        <is>
+          <t>Class A</t>
+        </is>
+      </c>
+      <c r="M21" s="9" t="inlineStr">
+        <is>
+          <t>Luxury</t>
+        </is>
+      </c>
+      <c r="N21" s="12" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="O21" s="12" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="P21" s="12" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="Q21" s="10" t="n">
+        <v>3393800</v>
+      </c>
+      <c r="R21" s="10" t="n">
+        <v>970</v>
+      </c>
+      <c r="S21" s="12" t="n">
+        <v>221.81</v>
+      </c>
+      <c r="T21" s="9" t="inlineStr">
+        <is>
+          <t>Downtown West</t>
+        </is>
+      </c>
+      <c r="U21" s="12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V21" s="9" t="inlineStr">
+        <is>
+          <t>Wood Frame</t>
+        </is>
+      </c>
+      <c r="W21" s="12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X21" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y21" s="10" t="n">
+        <v>1960</v>
+      </c>
+      <c r="Z21" s="12" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AA21" s="12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AB21" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC21" s="12" t="n">
+        <v>9.140000000000001</v>
+      </c>
+      <c r="AD21" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE21" s="9" t="inlineStr">
+        <is>
+          <t>Arm's Length</t>
+        </is>
+      </c>
+      <c r="AF21" s="9" t="inlineStr">
+        <is>
+          <t>Institutional</t>
+        </is>
+      </c>
+      <c r="AG21" s="9" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Liberty Landing</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>333 Freedom Way</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Springfield</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>62703</v>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>2022-06-03</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>59500000</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>295</v>
+      </c>
+      <c r="I22" s="7" t="n">
+        <v>201694.92</v>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>2007</v>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>2018</v>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>Class B+</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>Mid-Market</t>
+        </is>
+      </c>
+      <c r="N22" s="7" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="O22" s="7" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="P22" s="7" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="Q22" s="5" t="n">
+        <v>3225000</v>
+      </c>
+      <c r="R22" s="5" t="n">
+        <v>900</v>
+      </c>
+      <c r="S22" s="7" t="n">
+        <v>224.11</v>
+      </c>
+      <c r="T22" s="4" t="inlineStr">
+        <is>
+          <t>Southwest Crossing</t>
+        </is>
+      </c>
+      <c r="U22" s="7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V22" s="4" t="inlineStr">
+        <is>
+          <t>Wood Frame</t>
+        </is>
+      </c>
+      <c r="W22" s="7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X22" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y22" s="5" t="n">
+        <v>1730</v>
+      </c>
+      <c r="Z22" s="7" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AA22" s="7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AB22" s="7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC22" s="7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD22" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE22" s="4" t="inlineStr">
+        <is>
+          <t>Arm's Length</t>
+        </is>
+      </c>
+      <c r="AF22" s="4" t="inlineStr">
+        <is>
+          <t>REIT</t>
+        </is>
+      </c>
+      <c r="AG22" s="4" t="inlineStr">
+        <is>
+          <t>Individual</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>The District Lofts</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>666 Main St</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Springfield</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>62704</v>
+      </c>
+      <c r="F23" s="11" t="inlineStr">
+        <is>
+          <t>2022-05-20</t>
+        </is>
+      </c>
+      <c r="G23" s="10" t="n">
+        <v>64000000</v>
+      </c>
+      <c r="H23" s="10" t="n">
+        <v>280</v>
+      </c>
+      <c r="I23" s="12" t="n">
+        <v>228571.43</v>
+      </c>
+      <c r="J23" s="10" t="n">
+        <v>2021</v>
+      </c>
+      <c r="K23" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L23" s="9" t="inlineStr">
+        <is>
+          <t>Class A</t>
+        </is>
+      </c>
+      <c r="M23" s="9" t="inlineStr">
+        <is>
+          <t>Luxury</t>
+        </is>
+      </c>
+      <c r="N23" s="12" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="O23" s="12" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="P23" s="12" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="Q23" s="10" t="n">
+        <v>2995200</v>
+      </c>
+      <c r="R23" s="10" t="n">
+        <v>940</v>
+      </c>
+      <c r="S23" s="12" t="n">
+        <v>243.16</v>
+      </c>
+      <c r="T23" s="9" t="inlineStr">
+        <is>
+          <t>Midtown Core</t>
+        </is>
+      </c>
+      <c r="U23" s="12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="V23" s="9" t="inlineStr">
+        <is>
+          <t>Steel Frame</t>
+        </is>
+      </c>
+      <c r="W23" s="12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X23" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y23" s="10" t="n">
+        <v>2080</v>
+      </c>
+      <c r="Z23" s="12" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AA23" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB23" s="12" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC23" s="12" t="n">
+        <v>8.76</v>
+      </c>
+      <c r="AD23" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE23" s="9" t="inlineStr">
+        <is>
+          <t>Arm's Length</t>
+        </is>
+      </c>
+      <c r="AF23" s="9" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="AG23" s="9" t="inlineStr">
+        <is>
+          <t>Developer</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Pioneer Place</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>999 Explorer Ave</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Springfield</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>62708</v>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>2022-04-10</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>73000000</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>335</v>
+      </c>
+      <c r="I24" s="7" t="n">
+        <v>217910.45</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>2017</v>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>2022</v>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>Class A</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>Luxury</t>
+        </is>
+      </c>
+      <c r="N24" s="7" t="n">
+        <v>96</v>
+      </c>
+      <c r="O24" s="7" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="P24" s="7" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="Q24" s="5" t="n">
+        <v>3540500</v>
+      </c>
+      <c r="R24" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="S24" s="7" t="n">
+        <v>217.91</v>
+      </c>
+      <c r="T24" s="4" t="inlineStr">
+        <is>
+          <t>Northwood Central</t>
+        </is>
+      </c>
+      <c r="U24" s="7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="V24" s="4" t="inlineStr">
+        <is>
+          <t>Wood Frame</t>
+        </is>
+      </c>
+      <c r="W24" s="7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X24" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y24" s="5" t="n">
+        <v>1970</v>
+      </c>
+      <c r="Z24" s="7" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AA24" s="7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AB24" s="7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC24" s="7" t="n">
+        <v>9.24</v>
+      </c>
+      <c r="AD24" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE24" s="4" t="inlineStr">
+        <is>
+          <t>Arm's Length</t>
+        </is>
+      </c>
+      <c r="AF24" s="4" t="inlineStr">
+        <is>
+          <t>Institutional</t>
+        </is>
+      </c>
+      <c r="AG24" s="4" t="inlineStr">
+        <is>
+          <t>Institutional</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Maplewood Manor</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>222 Elmwood Cir</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>Springfield</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>62707</v>
+      </c>
+      <c r="F25" s="11" t="inlineStr">
+        <is>
+          <t>2022-03-25</t>
+        </is>
+      </c>
+      <c r="G25" s="10" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="H25" s="10" t="n">
+        <v>255</v>
+      </c>
+      <c r="I25" s="12" t="n">
+        <v>196078.43</v>
+      </c>
+      <c r="J25" s="10" t="n">
+        <v>1990</v>
+      </c>
+      <c r="K25" s="10" t="n">
+        <v>2014</v>
+      </c>
+      <c r="L25" s="9" t="inlineStr">
+        <is>
+          <t>Class C+</t>
+        </is>
+      </c>
+      <c r="M25" s="9" t="inlineStr">
+        <is>
+          <t>Workforce</t>
+        </is>
+      </c>
+      <c r="N25" s="12" t="n">
+        <v>91.5</v>
+      </c>
+      <c r="O25" s="12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="P25" s="12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Q25" s="10" t="n">
+        <v>3100000</v>
+      </c>
+      <c r="R25" s="10" t="n">
+        <v>870</v>
+      </c>
+      <c r="S25" s="12" t="n">
+        <v>225.38</v>
+      </c>
+      <c r="T25" s="9" t="inlineStr">
+        <is>
+          <t>Uptown South</t>
+        </is>
+      </c>
+      <c r="U25" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="V25" s="9" t="inlineStr">
+        <is>
+          <t>Brick</t>
+        </is>
+      </c>
+      <c r="W25" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="X25" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y25" s="10" t="n">
+        <v>1380</v>
+      </c>
+      <c r="Z25" s="12" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AA25" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB25" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC25" s="12" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="AD25" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE25" s="9" t="inlineStr">
+        <is>
+          <t>Arm's Length</t>
+        </is>
+      </c>
+      <c r="AF25" s="9" t="inlineStr">
+        <is>
+          <t>Individual</t>
+        </is>
+      </c>
+      <c r="AG25" s="9" t="inlineStr">
+        <is>
+          <t>Individual</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Stonecreek Commons</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>77 River Bend Rd</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Springfield</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>62701</v>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>2022-02-18</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>60000000</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>290</v>
+      </c>
+      <c r="I26" s="7" t="n">
+        <v>206896.55</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>2015</v>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>2021</v>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>Class B+</t>
+        </is>
+      </c>
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>Mid-Market</t>
+        </is>
+      </c>
+      <c r="N26" s="7" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="O26" s="7" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="P26" s="7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="Q26" s="5" t="n">
+        <v>3090000</v>
+      </c>
+      <c r="R26" s="5" t="n">
+        <v>930</v>
+      </c>
+      <c r="S26" s="7" t="n">
+        <v>222.47</v>
+      </c>
+      <c r="T26" s="4" t="inlineStr">
+        <is>
+          <t>Downtown East</t>
+        </is>
+      </c>
+      <c r="U26" s="7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V26" s="4" t="inlineStr">
+        <is>
+          <t>Wood Frame</t>
+        </is>
+      </c>
+      <c r="W26" s="7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X26" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y26" s="5" t="n">
+        <v>1760</v>
+      </c>
+      <c r="Z26" s="7" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AA26" s="7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AB26" s="7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC26" s="7" t="n">
+        <v>9.869999999999999</v>
+      </c>
+      <c r="AD26" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE26" s="4" t="inlineStr">
+        <is>
+          <t>Arm's Length</t>
+        </is>
+      </c>
+      <c r="AF26" s="4" t="inlineStr">
+        <is>
+          <t>REIT</t>
+        </is>
+      </c>
+      <c r="AG26" s="4" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>Canyon Creek Apartments</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>12 Stream Ct</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>Springfield</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>62703</v>
+      </c>
+      <c r="F27" s="11" t="inlineStr">
+        <is>
+          <t>2022-01-05</t>
+        </is>
+      </c>
+      <c r="G27" s="10" t="n">
+        <v>57000000</v>
+      </c>
+      <c r="H27" s="10" t="n">
+        <v>270</v>
+      </c>
+      <c r="I27" s="12" t="n">
+        <v>211111.11</v>
+      </c>
+      <c r="J27" s="10" t="n">
+        <v>2009</v>
+      </c>
+      <c r="K27" s="10" t="n">
+        <v>2019</v>
+      </c>
+      <c r="L27" s="9" t="inlineStr">
+        <is>
+          <t>Class B+</t>
+        </is>
+      </c>
+      <c r="M27" s="9" t="inlineStr">
+        <is>
+          <t>Mid-Market</t>
+        </is>
+      </c>
+      <c r="N27" s="12" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="O27" s="12" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="P27" s="12" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="Q27" s="10" t="n">
+        <v>3021000</v>
+      </c>
+      <c r="R27" s="10" t="n">
+        <v>900</v>
+      </c>
+      <c r="S27" s="12" t="n">
+        <v>234.57</v>
+      </c>
+      <c r="T27" s="9" t="inlineStr">
+        <is>
+          <t>Southside Park</t>
+        </is>
+      </c>
+      <c r="U27" s="12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V27" s="9" t="inlineStr">
+        <is>
+          <t>Wood Frame</t>
+        </is>
+      </c>
+      <c r="W27" s="12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X27" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y27" s="10" t="n">
+        <v>1710</v>
+      </c>
+      <c r="Z27" s="12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA27" s="12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AB27" s="12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC27" s="12" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="AD27" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE27" s="9" t="inlineStr">
+        <is>
+          <t>Arm's Length</t>
+        </is>
+      </c>
+      <c r="AF27" s="9" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="AG27" s="9" t="inlineStr">
+        <is>
+          <t>Individual</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Pinehurst Gardens</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>505 Pine St</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Springfield</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>62708</v>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>2021-12-15</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>69000000</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>325</v>
+      </c>
+      <c r="I28" s="7" t="n">
+        <v>212307.69</v>
+      </c>
+      <c r="J28" s="5" t="n">
+        <v>2016</v>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>Class A</t>
+        </is>
+      </c>
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>Luxury</t>
+        </is>
+      </c>
+      <c r="N28" s="7" t="n">
+        <v>97</v>
+      </c>
+      <c r="O28" s="7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P28" s="7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="Q28" s="5" t="n">
+        <v>3381000</v>
+      </c>
+      <c r="R28" s="5" t="n">
+        <v>980</v>
+      </c>
+      <c r="S28" s="7" t="n">
+        <v>216.64</v>
+      </c>
+      <c r="T28" s="4" t="inlineStr">
+        <is>
+          <t>Northwood Vista</t>
+        </is>
+      </c>
+      <c r="U28" s="7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="V28" s="4" t="inlineStr">
+        <is>
+          <t>Wood Frame</t>
+        </is>
+      </c>
+      <c r="W28" s="7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X28" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y28" s="5" t="n">
+        <v>1930</v>
+      </c>
+      <c r="Z28" s="7" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AA28" s="7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AB28" s="7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC28" s="7" t="n">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="AD28" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE28" s="4" t="inlineStr">
+        <is>
+          <t>Arm's Length</t>
+        </is>
+      </c>
+      <c r="AF28" s="4" t="inlineStr">
+        <is>
+          <t>Institutional</t>
+        </is>
+      </c>
+      <c r="AG28" s="4" t="inlineStr">
+        <is>
+          <t>Developer</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>Sunset Ridge</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>606 Horizon Dr</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>Springfield</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>62707</v>
+      </c>
+      <c r="F29" s="11" t="inlineStr">
+        <is>
+          <t>2021-11-01</t>
+        </is>
+      </c>
+      <c r="G29" s="10" t="n">
+        <v>55000000</v>
+      </c>
+      <c r="H29" s="10" t="n">
+        <v>270</v>
+      </c>
+      <c r="I29" s="12" t="n">
+        <v>203703.7</v>
+      </c>
+      <c r="J29" s="10" t="n">
+        <v>2006</v>
+      </c>
+      <c r="K29" s="10" t="n">
+        <v>2017</v>
+      </c>
+      <c r="L29" s="9" t="inlineStr">
+        <is>
+          <t>Class B</t>
+        </is>
+      </c>
+      <c r="M29" s="9" t="inlineStr">
+        <is>
+          <t>Mid-Market</t>
+        </is>
+      </c>
+      <c r="N29" s="12" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="O29" s="12" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="P29" s="12" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="Q29" s="10" t="n">
+        <v>3135000</v>
+      </c>
+      <c r="R29" s="10" t="n">
+        <v>890</v>
+      </c>
+      <c r="S29" s="12" t="n">
+        <v>228.85</v>
+      </c>
+      <c r="T29" s="9" t="inlineStr">
+        <is>
+          <t>Uptown Ridge</t>
+        </is>
+      </c>
+      <c r="U29" s="12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V29" s="9" t="inlineStr">
+        <is>
+          <t>Wood Frame</t>
+        </is>
+      </c>
+      <c r="W29" s="12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X29" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y29" s="10" t="n">
+        <v>1650</v>
+      </c>
+      <c r="Z29" s="12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA29" s="12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB29" s="12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AC29" s="12" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="AD29" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE29" s="9" t="inlineStr">
+        <is>
+          <t>Arm's Length</t>
+        </is>
+      </c>
+      <c r="AF29" s="9" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="AG29" s="9" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Evergreen Place</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>100 Evergreen Ln</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Springfield</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>62704</v>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>2021-10-10</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>61000000</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>285</v>
+      </c>
+      <c r="I30" s="7" t="n">
+        <v>214035.09</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>2019</v>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>Class A</t>
+        </is>
+      </c>
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>Mid-Market</t>
+        </is>
+      </c>
+      <c r="N30" s="7" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="O30" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="P30" s="7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="Q30" s="5" t="n">
+        <v>3050000</v>
+      </c>
+      <c r="R30" s="5" t="n">
+        <v>950</v>
+      </c>
+      <c r="S30" s="7" t="n">
+        <v>225.3</v>
+      </c>
+      <c r="T30" s="4" t="inlineStr">
+        <is>
+          <t>Midtown East</t>
+        </is>
+      </c>
+      <c r="U30" s="7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="V30" s="4" t="inlineStr">
+        <is>
+          <t>Wood Frame</t>
+        </is>
+      </c>
+      <c r="W30" s="7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X30" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y30" s="5" t="n">
+        <v>1850</v>
+      </c>
+      <c r="Z30" s="7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA30" s="7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AB30" s="7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC30" s="7" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="AD30" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE30" s="4" t="inlineStr">
+        <is>
+          <t>Arm's Length</t>
+        </is>
+      </c>
+      <c r="AF30" s="4" t="inlineStr">
+        <is>
+          <t>REIT</t>
+        </is>
+      </c>
+      <c r="AG30" s="4" t="inlineStr">
+        <is>
+          <t>Developer</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>Willowbrook Park</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>202 Brookside Ave</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>Springfield</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>62701</v>
+      </c>
+      <c r="F31" s="11" t="inlineStr">
+        <is>
+          <t>2021-09-05</t>
+        </is>
+      </c>
+      <c r="G31" s="10" t="n">
+        <v>49000000</v>
+      </c>
+      <c r="H31" s="10" t="n">
+        <v>230</v>
+      </c>
+      <c r="I31" s="12" t="n">
+        <v>213043.48</v>
+      </c>
+      <c r="J31" s="10" t="n">
+        <v>1992</v>
+      </c>
+      <c r="K31" s="10" t="n">
+        <v>2015</v>
+      </c>
+      <c r="L31" s="9" t="inlineStr">
+        <is>
+          <t>Class B</t>
+        </is>
+      </c>
+      <c r="M31" s="9" t="inlineStr">
+        <is>
+          <t>Workforce</t>
+        </is>
+      </c>
+      <c r="N31" s="12" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="O31" s="12" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="P31" s="12" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="Q31" s="10" t="n">
+        <v>2891000</v>
+      </c>
+      <c r="R31" s="10" t="n">
+        <v>860</v>
+      </c>
+      <c r="S31" s="12" t="n">
+        <v>247.72</v>
+      </c>
+      <c r="T31" s="9" t="inlineStr">
+        <is>
+          <t>Downtown South</t>
+        </is>
+      </c>
+      <c r="U31" s="12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V31" s="9" t="inlineStr">
+        <is>
+          <t>Brick</t>
+        </is>
+      </c>
+      <c r="W31" s="12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X31" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y31" s="10" t="n">
+        <v>1480</v>
+      </c>
+      <c r="Z31" s="12" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AA31" s="12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB31" s="12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AC31" s="12" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="AD31" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE31" s="9" t="inlineStr">
+        <is>
+          <t>Arm's Length</t>
+        </is>
+      </c>
+      <c r="AF31" s="9" t="inlineStr">
+        <is>
+          <t>Individual</t>
+        </is>
+      </c>
+      <c r="AG31" s="9" t="inlineStr">
+        <is>
+          <t>Individual</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Fairway Residences</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>303 Golf Course Rd</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Springfield</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>62708</v>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>2021-08-20</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>76000000</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>345</v>
+      </c>
+      <c r="I32" s="7" t="n">
+        <v>220289.86</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>2020</v>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>Class A</t>
+        </is>
+      </c>
+      <c r="M32" s="4" t="inlineStr">
+        <is>
+          <t>Luxury</t>
+        </is>
+      </c>
+      <c r="N32" s="7" t="n">
+        <v>97</v>
+      </c>
+      <c r="O32" s="7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P32" s="7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Q32" s="5" t="n">
+        <v>3496000</v>
+      </c>
+      <c r="R32" s="5" t="n">
+        <v>1030</v>
+      </c>
+      <c r="S32" s="7" t="n">
+        <v>213.87</v>
+      </c>
+      <c r="T32" s="4" t="inlineStr">
+        <is>
+          <t>Northwood Green</t>
+        </is>
+      </c>
+      <c r="U32" s="7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="V32" s="4" t="inlineStr">
+        <is>
+          <t>Wood Frame</t>
+        </is>
+      </c>
+      <c r="W32" s="7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X32" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y32" s="5" t="n">
+        <v>2010</v>
+      </c>
+      <c r="Z32" s="7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA32" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB32" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC32" s="7" t="n">
+        <v>9.130000000000001</v>
+      </c>
+      <c r="AD32" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE32" s="4" t="inlineStr">
+        <is>
+          <t>Arm's Length</t>
+        </is>
+      </c>
+      <c r="AF32" s="4" t="inlineStr">
+        <is>
+          <t>Institutional</t>
+        </is>
+      </c>
+      <c r="AG32" s="4" t="inlineStr">
+        <is>
+          <t>Developer</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>Highland Crossings</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>404 Hilltop View</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>Springfield</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="E33" s="10" t="n">
+        <v>62703</v>
+      </c>
+      <c r="F33" s="11" t="inlineStr">
+        <is>
+          <t>2021-07-15</t>
+        </is>
+      </c>
+      <c r="G33" s="10" t="n">
+        <v>66000000</v>
+      </c>
+      <c r="H33" s="10" t="n">
+        <v>310</v>
+      </c>
+      <c r="I33" s="12" t="n">
+        <v>212903.23</v>
+      </c>
+      <c r="J33" s="10" t="n">
+        <v>2012</v>
+      </c>
+      <c r="K33" s="10" t="n">
+        <v>2020</v>
+      </c>
+      <c r="L33" s="9" t="inlineStr">
+        <is>
+          <t>Class B+</t>
+        </is>
+      </c>
+      <c r="M33" s="9" t="inlineStr">
+        <is>
+          <t>Mid-Market</t>
+        </is>
+      </c>
+      <c r="N33" s="12" t="n">
+        <v>95</v>
+      </c>
+      <c r="O33" s="12" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="P33" s="12" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="Q33" s="10" t="n">
+        <v>3465000</v>
+      </c>
+      <c r="R33" s="10" t="n">
+        <v>920</v>
+      </c>
+      <c r="S33" s="12" t="n">
+        <v>231.42</v>
+      </c>
+      <c r="T33" s="9" t="inlineStr">
+        <is>
+          <t>South Ridge</t>
+        </is>
+      </c>
+      <c r="U33" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="V33" s="9" t="inlineStr">
+        <is>
+          <t>Wood Frame</t>
+        </is>
+      </c>
+      <c r="W33" s="12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X33" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y33" s="10" t="n">
+        <v>1800</v>
+      </c>
+      <c r="Z33" s="12" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AA33" s="12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB33" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC33" s="12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD33" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE33" s="9" t="inlineStr">
+        <is>
+          <t>Arm's Length</t>
+        </is>
+      </c>
+      <c r="AF33" s="9" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="AG33" s="9" t="inlineStr">
+        <is>
+          <t>REIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Springfield Gardens</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>707 Garden Rd</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Springfield</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>62707</v>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>2021-06-01</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>52000000</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>260</v>
+      </c>
+      <c r="I34" s="7" t="n">
+        <v>200000</v>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>2001</v>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>2016</v>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>Class B</t>
+        </is>
+      </c>
+      <c r="M34" s="4" t="inlineStr">
+        <is>
+          <t>Mid-Market</t>
+        </is>
+      </c>
+      <c r="N34" s="7" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="O34" s="7" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="P34" s="7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="Q34" s="5" t="n">
+        <v>2886000</v>
+      </c>
+      <c r="R34" s="5" t="n">
+        <v>890</v>
+      </c>
+      <c r="S34" s="7" t="n">
+        <v>223.11</v>
+      </c>
+      <c r="T34" s="4" t="inlineStr">
+        <is>
+          <t>Uptown Central</t>
+        </is>
+      </c>
+      <c r="U34" s="7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V34" s="4" t="inlineStr">
+        <is>
+          <t>Wood Frame</t>
+        </is>
+      </c>
+      <c r="W34" s="7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X34" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y34" s="5" t="n">
+        <v>1620</v>
+      </c>
+      <c r="Z34" s="7" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AA34" s="7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB34" s="7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC34" s="7" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="AD34" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE34" s="4" t="inlineStr">
+        <is>
+          <t>Arm's Length</t>
+        </is>
+      </c>
+      <c r="AF34" s="4" t="inlineStr">
+        <is>
+          <t>Individual</t>
+        </is>
+      </c>
+      <c r="AG34" s="4" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>The Boulevard</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>818 Blvd Way</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>Springfield</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>62704</v>
+      </c>
+      <c r="F35" s="11" t="inlineStr">
+        <is>
+          <t>2021-05-18</t>
+        </is>
+      </c>
+      <c r="G35" s="10" t="n">
+        <v>63000000</v>
+      </c>
+      <c r="H35" s="10" t="n">
+        <v>290</v>
+      </c>
+      <c r="I35" s="12" t="n">
+        <v>217241.38</v>
+      </c>
+      <c r="J35" s="10" t="n">
+        <v>2017</v>
+      </c>
+      <c r="K35" s="10" t="n">
+        <v>2022</v>
+      </c>
+      <c r="L35" s="9" t="inlineStr">
+        <is>
+          <t>Class A</t>
+        </is>
+      </c>
+      <c r="M35" s="9" t="inlineStr">
+        <is>
+          <t>Mid-Market</t>
+        </is>
+      </c>
+      <c r="N35" s="12" t="n">
+        <v>96</v>
+      </c>
+      <c r="O35" s="12" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="P35" s="12" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="Q35" s="10" t="n">
+        <v>3118500</v>
+      </c>
+      <c r="R35" s="10" t="n">
+        <v>940</v>
+      </c>
+      <c r="S35" s="12" t="n">
+        <v>230.9</v>
+      </c>
+      <c r="T35" s="9" t="inlineStr">
+        <is>
+          <t>Midtown South</t>
+        </is>
+      </c>
+      <c r="U35" s="12" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V35" s="9" t="inlineStr">
+        <is>
+          <t>Steel Frame</t>
+        </is>
+      </c>
+      <c r="W35" s="12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X35" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y35" s="10" t="n">
+        <v>1880</v>
+      </c>
+      <c r="Z35" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA35" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB35" s="12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC35" s="12" t="n">
+        <v>9.66</v>
+      </c>
+      <c r="AD35" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE35" s="9" t="inlineStr">
+        <is>
+          <t>Arm's Length</t>
+        </is>
+      </c>
+      <c r="AF35" s="9" t="inlineStr">
+        <is>
+          <t>REIT</t>
+        </is>
+      </c>
+      <c r="AG35" s="9" t="inlineStr">
+        <is>
+          <t>Institutional</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Urban Pointe</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>909 City View</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Springfield</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>62701</v>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>2021-04-03</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>70000000</v>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>315</v>
+      </c>
+      <c r="I36" s="7" t="n">
+        <v>222222.22</v>
+      </c>
+      <c r="J36" s="5" t="n">
+        <v>2022</v>
+      </c>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>Class A</t>
+        </is>
+      </c>
+      <c r="M36" s="4" t="inlineStr">
+        <is>
+          <t>Luxury</t>
+        </is>
+      </c>
+      <c r="N36" s="7" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="O36" s="7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="P36" s="7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Q36" s="5" t="n">
+        <v>3290000</v>
+      </c>
+      <c r="R36" s="5" t="n">
+        <v>960</v>
+      </c>
+      <c r="S36" s="7" t="n">
+        <v>231.48</v>
+      </c>
+      <c r="T36" s="4" t="inlineStr">
+        <is>
+          <t>Downtown West</t>
+        </is>
+      </c>
+      <c r="U36" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V36" s="4" t="inlineStr">
+        <is>
+          <t>Concrete</t>
+        </is>
+      </c>
+      <c r="W36" s="7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X36" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y36" s="5" t="n">
+        <v>1990</v>
+      </c>
+      <c r="Z36" s="7" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AA36" s="7" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="AB36" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC36" s="7" t="n">
+        <v>9.32</v>
+      </c>
+      <c r="AD36" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE36" s="4" t="inlineStr">
+        <is>
+          <t>Arm's Length</t>
+        </is>
+      </c>
+      <c r="AF36" s="4" t="inlineStr">
+        <is>
+          <t>Institutional</t>
+        </is>
+      </c>
+      <c r="AG36" s="4" t="inlineStr">
+        <is>
+          <t>Developer</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>Centennial Place</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>100 Year St</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>Springfield</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>62703</v>
+      </c>
+      <c r="F37" s="11" t="inlineStr">
+        <is>
+          <t>2021-03-20</t>
+        </is>
+      </c>
+      <c r="G37" s="10" t="n">
+        <v>58000000</v>
+      </c>
+      <c r="H37" s="10" t="n">
+        <v>280</v>
+      </c>
+      <c r="I37" s="12" t="n">
+        <v>207142.86</v>
+      </c>
+      <c r="J37" s="10" t="n">
+        <v>2008</v>
+      </c>
+      <c r="K37" s="10" t="n">
+        <v>2018</v>
+      </c>
+      <c r="L37" s="9" t="inlineStr">
+        <is>
+          <t>Class B+</t>
+        </is>
+      </c>
+      <c r="M37" s="9" t="inlineStr">
+        <is>
+          <t>Mid-Market</t>
+        </is>
+      </c>
+      <c r="N37" s="12" t="n">
+        <v>94</v>
+      </c>
+      <c r="O37" s="12" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="P37" s="12" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="Q37" s="10" t="n">
+        <v>3132000</v>
+      </c>
+      <c r="R37" s="10" t="n">
+        <v>910</v>
+      </c>
+      <c r="S37" s="12" t="n">
+        <v>227.63</v>
+      </c>
+      <c r="T37" s="9" t="inlineStr">
+        <is>
+          <t>South End</t>
+        </is>
+      </c>
+      <c r="U37" s="12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="V37" s="9" t="inlineStr">
+        <is>
+          <t>Wood Frame</t>
+        </is>
+      </c>
+      <c r="W37" s="12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X37" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y37" s="10" t="n">
+        <v>1740</v>
+      </c>
+      <c r="Z37" s="12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA37" s="12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB37" s="12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC37" s="12" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="AD37" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE37" s="9" t="inlineStr">
+        <is>
+          <t>Arm's Length</t>
+        </is>
+      </c>
+      <c r="AF37" s="9" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="AG37" s="9" t="inlineStr">
+        <is>
+          <t>Individual</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Northwood Park</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>150 Forest Dr</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Springfield</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>62708</v>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>2021-02-05</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>74000000</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>330</v>
+      </c>
+      <c r="I38" s="7" t="n">
+        <v>224242.42</v>
+      </c>
+      <c r="J38" s="5" t="n">
+        <v>2019</v>
+      </c>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t>Class A</t>
+        </is>
+      </c>
+      <c r="M38" s="4" t="inlineStr">
+        <is>
+          <t>Luxury</t>
+        </is>
+      </c>
+      <c r="N38" s="7" t="n">
+        <v>98</v>
+      </c>
+      <c r="O38" s="7" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="P38" s="7" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="Q38" s="5" t="n">
+        <v>3441000</v>
+      </c>
+      <c r="R38" s="5" t="n">
+        <v>1010</v>
+      </c>
+      <c r="S38" s="7" t="n">
+        <v>221.9</v>
+      </c>
+      <c r="T38" s="4" t="inlineStr">
+        <is>
+          <t>Northwood East</t>
+        </is>
+      </c>
+      <c r="U38" s="7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="V38" s="4" t="inlineStr">
+        <is>
+          <t>Wood Frame</t>
+        </is>
+      </c>
+      <c r="W38" s="7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X38" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y38" s="5" t="n">
+        <v>2030</v>
+      </c>
+      <c r="Z38" s="7" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AA38" s="7" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AB38" s="7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC38" s="7" t="n">
+        <v>9.130000000000001</v>
+      </c>
+      <c r="AD38" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE38" s="4" t="inlineStr">
+        <is>
+          <t>Arm's Length</t>
+        </is>
+      </c>
+      <c r="AF38" s="4" t="inlineStr">
+        <is>
+          <t>Institutional</t>
+        </is>
+      </c>
+      <c r="AG38" s="4" t="inlineStr">
+        <is>
+          <t>Developer</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AG38"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:AG1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>